--- a/MT4_UM2.xlsx
+++ b/MT4_UM2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yiming.chong\Documents\GitHub\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6431972-99DD-45E0-8DD8-36EF02CF9FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E85906A-D561-4C2C-8E6A-80C0085A023A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71895" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Forex1" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="52">
   <si>
     <t>CompanyName</t>
   </si>
@@ -519,22 +519,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -593,7 +593,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -649,6 +649,242 @@
         <v>31</v>
       </c>
       <c r="S2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1052</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>22</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1052</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>22</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1052</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>22</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1052</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>22</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -660,22 +896,22 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24A97939-2805-41FD-B680-B53CD297F10A}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -734,7 +970,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -790,6 +1026,242 @@
         <v>49</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1052</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>32</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>22</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>15</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>49</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1052</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>32</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>22</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>15</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1052</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>32</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>22</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>15</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1052</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>32</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>22</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>15</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>49</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -801,22 +1273,22 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50532A11-BB1D-4F26-BBEE-FF3CAFF17BE2}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -875,7 +1347,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -931,6 +1403,242 @@
         <v>51</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1052</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>33</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>21</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3">
+        <v>45</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1052</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>33</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>21</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
+        <v>45</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>51</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1052</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>33</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>21</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>45</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>51</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1052</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>33</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>21</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>45</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>51</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -942,22 +1650,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DBFB7EA-40D2-4AEF-AE16-9C6A9ACF0727}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1016,7 +1724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1072,6 +1780,242 @@
         <v>33</v>
       </c>
       <c r="S2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1052</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>26</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1052</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>26</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1052</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>26</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R5" t="s">
+        <v>33</v>
+      </c>
+      <c r="S5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1052</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1083,22 +2027,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86B2852-C16D-4326-8626-1C545ED09338}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1157,7 +2101,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1213,6 +2157,242 @@
         <v>35</v>
       </c>
       <c r="S2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1052</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>24</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1052</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>24</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1052</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>24</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R5" t="s">
+        <v>35</v>
+      </c>
+      <c r="S5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1052</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>24</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R6" t="s">
+        <v>35</v>
+      </c>
+      <c r="S6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1224,22 +2404,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2ABB095-35F2-4820-BA7D-AACDF5AC29ED}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1298,7 +2478,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1354,6 +2534,242 @@
         <v>37</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1052</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>25</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1052</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>25</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>37</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1052</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>25</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1052</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>25</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1365,22 +2781,22 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8A64BA9-AE49-4601-BDB8-368EE6FA41C6}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1439,7 +2855,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1495,6 +2911,242 @@
         <v>39</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1052</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>27</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1052</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>27</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>39</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1052</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>27</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1052</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>27</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>39</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1506,22 +3158,22 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644856BC-020F-4C9A-8C44-C2C911A21A97}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1580,7 +3232,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1636,6 +3288,242 @@
         <v>41</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1052</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>28</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>20</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>45</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1052</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>28</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>20</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>45</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1052</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>28</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>20</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>45</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1052</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>28</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>20</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>45</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>41</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1647,22 +3535,22 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F213CA8B-C6C2-4E7B-A814-8A18CEB0E85C}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1721,7 +3609,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1777,6 +3665,242 @@
         <v>43</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1052</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>29</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1052</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>29</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1052</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>29</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1052</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>29</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>43</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1788,22 +3912,22 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A58BA4B6-30AC-4566-AC69-57CCCF3E997A}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1862,7 +3986,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1918,6 +4042,242 @@
         <v>45</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1052</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>30</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>45</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1052</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>30</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>45</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1052</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>30</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>23</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>45</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>45</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1052</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>30</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>23</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>45</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1929,22 +4289,22 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C27AB6-C119-4240-85FC-9A3D905F4959}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2003,7 +4363,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -2059,6 +4419,242 @@
         <v>47</v>
       </c>
       <c r="S2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1052</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3">
+        <v>31</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>22</v>
+      </c>
+      <c r="N3">
+        <v>9</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>1052</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>31</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>22</v>
+      </c>
+      <c r="N4">
+        <v>9</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>1052</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5">
+        <v>31</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>22</v>
+      </c>
+      <c r="N5">
+        <v>9</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>47</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>1052</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>31</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>22</v>
+      </c>
+      <c r="N6">
+        <v>9</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>47</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
